--- a/planning tm.xlsx
+++ b/planning tm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://erzbe-my.sharepoint.com/personal/bilal_bertolini_edu_gbjb_ch/Documents/école/TM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\jeu-unity\dossier-TM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="8_{0340B08F-4292-4A48-B1F2-CDB6C4BE3943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{770FF421-1012-41A7-8186-7643DE0DAC2D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12224AC3-2DFE-4F9B-9A84-C0366C120B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1410" yWindow="1410" windowWidth="14400" windowHeight="8453" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11836" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>planning tm</t>
   </si>
@@ -101,9 +101,6 @@
     <t xml:space="preserve">coder le saut et l'attaque de base </t>
   </si>
   <si>
-    <t>planifier la suite du TM</t>
-  </si>
-  <si>
     <t>préparer présentation intermédiaire</t>
   </si>
   <si>
@@ -111,6 +108,12 @@
   </si>
   <si>
     <t>préparer quelques slides puis envoyer au menthor</t>
+  </si>
+  <si>
+    <t>avancer sur designs et animations</t>
+  </si>
+  <si>
+    <t>réfléchir au déroulement du jeu</t>
   </si>
 </sst>
 </file>
@@ -144,7 +147,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,6 +184,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -194,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -227,6 +236,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -268,10 +280,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -745,91 +753,99 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="B11" s="7">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D11" s="3"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
-        <v>46166</v>
+        <v>46159</v>
       </c>
       <c r="B12" s="7">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
-        <v>46173</v>
+        <v>46162</v>
       </c>
       <c r="B13" s="7">
+        <v>180</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>46165</v>
+      </c>
+      <c r="B14" s="7">
         <v>120</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="4">
-        <v>46178</v>
-      </c>
-      <c r="B14" s="7">
-        <v>5</v>
-      </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A15" s="4">
-        <v>46307</v>
-      </c>
-      <c r="B15" s="7"/>
+      <c r="A15" s="1">
+        <v>46166</v>
+      </c>
+      <c r="B15" s="7">
+        <v>120</v>
+      </c>
       <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
+        <v>46175</v>
+      </c>
+      <c r="B16" s="7">
+        <v>5</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" s="4">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" s="4">
         <v>46357</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B18" s="7">
         <v>30</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="1">
-        <v>46158</v>
-      </c>
-      <c r="B17" s="7">
-        <v>120</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B18" s="7"/>
-      <c r="C18" s="2"/>
       <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">

--- a/planning tm.xlsx
+++ b/planning tm.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\jeu-unity\dossier-TM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12224AC3-2DFE-4F9B-9A84-C0366C120B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF735CB0-82D4-407C-ABC7-731598AE00C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11836" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>planning tm</t>
   </si>
@@ -107,13 +107,16 @@
     <t>Implémenter gravité et terrain</t>
   </si>
   <si>
-    <t>préparer quelques slides puis envoyer au menthor</t>
-  </si>
-  <si>
     <t>avancer sur designs et animations</t>
   </si>
   <si>
     <t>réfléchir au déroulement du jeu</t>
+  </si>
+  <si>
+    <t>coder l'attaque de base</t>
+  </si>
+  <si>
+    <t>préparer les slides puis envoyer au menthor avec journal de bord et github     présentation de votre objectif, où vous en êtes, un ou deux résultats intermédiaires que vous voulez partager, les prochaines étapes et les difficultés / questions rencontrées</t>
   </si>
 </sst>
 </file>
@@ -147,7 +150,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -174,19 +177,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -232,13 +229,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -617,16 +614,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99B05EE-3531-444B-9158-CBFCD187C5CE}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="57.59765625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="45.53125" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="10.6640625" style="2"/>
+    <col min="1" max="1" width="30.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="57.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="45.5703125" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="10.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,7 +631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -651,7 +648,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>46054</v>
       </c>
@@ -662,7 +659,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46117</v>
       </c>
@@ -673,7 +670,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46144</v>
       </c>
@@ -684,7 +681,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46144</v>
       </c>
@@ -699,7 +696,7 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46145</v>
       </c>
@@ -712,7 +709,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>46149</v>
       </c>
@@ -723,9 +720,9 @@
         <v>6</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="11"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E8" s="10"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46149</v>
       </c>
@@ -738,7 +735,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46152</v>
       </c>
@@ -749,9 +746,9 @@
         <v>17</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E10" s="11"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46158</v>
       </c>
@@ -762,9 +759,9 @@
         <v>21</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="12"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E11" s="10"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46159</v>
       </c>
@@ -775,95 +772,106 @@
         <v>19</v>
       </c>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E12" s="6"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>46162</v>
+        <v>46166</v>
       </c>
       <c r="B13" s="7">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>46165</v>
+        <v>46172</v>
       </c>
       <c r="B14" s="7">
         <v>120</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>46166</v>
+        <v>46173</v>
       </c>
       <c r="B15" s="7">
+        <v>60</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="12"/>
+    </row>
+    <row r="16" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B16" s="7">
         <v>120</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A16" s="4">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
         <v>46175</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B17" s="7">
         <v>5</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A17" s="4">
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
         <v>46307</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="2" t="s">
+      <c r="B18" s="7"/>
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="4">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
         <v>46357</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B19" s="7">
         <v>30</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B19" s="7"/>
-      <c r="C19" s="2"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7"/>
       <c r="C20" s="2"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7"/>
       <c r="C21" s="2"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7"/>
       <c r="C22" s="2"/>
       <c r="D22" s="3"/>

--- a/planning tm.xlsx
+++ b/planning tm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\jeu-unity\dossier-TM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF735CB0-82D4-407C-ABC7-731598AE00C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D9B03D-0D30-4630-9394-70A0B4C0FD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11836" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
+    <workbookView xWindow="0" yWindow="585" windowWidth="19200" windowHeight="11055" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -149,8 +149,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -183,7 +190,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -200,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -235,7 +254,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -614,16 +639,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99B05EE-3531-444B-9158-CBFCD187C5CE}">
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="57.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="45.5703125" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="10.7109375" style="2"/>
+    <col min="1" max="1" width="30.265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.86328125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="57.59765625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="45.59765625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="10.73046875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,7 +656,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -648,7 +673,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="4">
         <v>46054</v>
       </c>
@@ -659,7 +684,7 @@
       <c r="D3" s="3"/>
       <c r="E3" s="6"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>46117</v>
       </c>
@@ -670,7 +695,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>46144</v>
       </c>
@@ -681,7 +706,7 @@
       <c r="D5" s="3"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>46144</v>
       </c>
@@ -696,7 +721,7 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>46145</v>
       </c>
@@ -709,7 +734,7 @@
       <c r="D7" s="3"/>
       <c r="E7" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="4">
         <v>46149</v>
       </c>
@@ -722,7 +747,7 @@
       <c r="D8" s="3"/>
       <c r="E8" s="10"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>46149</v>
       </c>
@@ -735,7 +760,7 @@
       <c r="D9" s="3"/>
       <c r="E9" s="9"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>46152</v>
       </c>
@@ -748,7 +773,7 @@
       <c r="D10" s="3"/>
       <c r="E10" s="11"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>46158</v>
       </c>
@@ -761,7 +786,7 @@
       <c r="D11" s="3"/>
       <c r="E11" s="10"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>46159</v>
       </c>
@@ -774,7 +799,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>46166</v>
       </c>
@@ -787,7 +812,7 @@
       <c r="D13" s="3"/>
       <c r="E13" s="9"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>46172</v>
       </c>
@@ -800,7 +825,7 @@
       <c r="D14" s="3"/>
       <c r="E14" s="12"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>46173</v>
       </c>
@@ -811,9 +836,9 @@
         <v>23</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="12"/>
-    </row>
-    <row r="16" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="E15" s="14"/>
+    </row>
+    <row r="16" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>46175</v>
       </c>
@@ -826,8 +851,9 @@
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>46175</v>
       </c>
@@ -839,7 +865,7 @@
       </c>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>46307</v>
       </c>
@@ -849,7 +875,7 @@
       </c>
       <c r="D18" s="3"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>46357</v>
       </c>
@@ -861,17 +887,17 @@
       </c>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B20" s="7"/>
       <c r="C20" s="2"/>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B21" s="7"/>
       <c r="C21" s="2"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B22" s="7"/>
       <c r="C22" s="2"/>
       <c r="D22" s="3"/>

--- a/planning tm.xlsx
+++ b/planning tm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\jeu-unity\dossier-TM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D9B03D-0D30-4630-9394-70A0B4C0FD24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE21AF4D-4AF9-42FA-A212-645FC8D5498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="585" windowWidth="19200" windowHeight="11055" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
+    <workbookView xWindow="0" yWindow="225" windowWidth="19200" windowHeight="11055" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>planning tm</t>
   </si>
@@ -117,6 +117,30 @@
   </si>
   <si>
     <t>préparer les slides puis envoyer au menthor avec journal de bord et github     présentation de votre objectif, où vous en êtes, un ou deux résultats intermédiaires que vous voulez partager, les prochaines étapes et les difficultés / questions rencontrées</t>
+  </si>
+  <si>
+    <t>implémenter animation de course sur unity</t>
+  </si>
+  <si>
+    <t>Ajouter attaque spéciale au premier personnage</t>
+  </si>
+  <si>
+    <t>animer saut et attaque de base</t>
+  </si>
+  <si>
+    <t>animer attaque spéciale au premier personnage</t>
+  </si>
+  <si>
+    <t>implémenter animation de saut et attaques sur unity</t>
+  </si>
+  <si>
+    <t>créer visuels avec vie des personnages etc.</t>
+  </si>
+  <si>
+    <t>terminer le script sur classe personnage</t>
+  </si>
+  <si>
+    <t>180 peut-être un peu plus en fait</t>
   </si>
 </sst>
 </file>
@@ -157,7 +181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,19 +214,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -219,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -261,6 +291,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -305,10 +344,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}" name="Tableau1" displayName="Tableau1" ref="A2:E22" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A2:E22" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E22">
-    <sortCondition ref="A2:A22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}" name="Tableau1" displayName="Tableau1" ref="A2:E26" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A2:E26" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E25">
+    <sortCondition ref="A2:A25"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{71A8CFFA-D8D8-4528-9B87-104437A98853}" name="date" dataDxfId="4"/>
@@ -638,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99B05EE-3531-444B-9158-CBFCD187C5CE}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="30.265625" style="1" customWidth="1"/>
@@ -836,7 +875,7 @@
         <v>23</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="13"/>
     </row>
     <row r="16" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
@@ -851,9 +890,9 @@
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>46175</v>
       </c>
@@ -864,43 +903,116 @@
         <v>12</v>
       </c>
       <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A18" s="4">
+      <c r="E17" s="9"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B18" s="7">
+        <v>120</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="14"/>
+    </row>
+    <row r="19" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
+        <v>46187</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="15"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
+        <v>46193</v>
+      </c>
+      <c r="B20" s="7">
+        <v>150</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="17"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B21" s="7">
+        <v>150</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="17"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B22" s="7">
+        <v>60</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="17"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B23" s="7">
+        <v>150</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="17"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A24" s="4">
         <v>46307</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="2" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="4">
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
         <v>46357</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B25" s="7">
         <v>30</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B20" s="7"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B21" s="7"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B22" s="7"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B26" s="7">
+        <v>60</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/planning tm.xlsx
+++ b/planning tm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\jeu-unity\dossier-TM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE21AF4D-4AF9-42FA-A212-645FC8D5498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76D569B-0851-415E-945F-F1E6FDFF1749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="225" windowWidth="19200" windowHeight="11055" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
+    <workbookView xWindow="15" yWindow="375" windowWidth="19185" windowHeight="10905" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -140,7 +140,7 @@
     <t>terminer le script sur classe personnage</t>
   </si>
   <si>
-    <t>180 peut-être un peu plus en fait</t>
+    <t>180 ou plus</t>
   </si>
 </sst>
 </file>
@@ -181,7 +181,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -236,6 +236,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -290,9 +296,6 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -300,6 +303,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -916,24 +922,24 @@
         <v>26</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="E18" s="17"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
-        <v>46187</v>
-      </c>
-      <c r="B19" s="16" t="s">
+        <v>46248</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="15"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
-        <v>46193</v>
+        <v>46250</v>
       </c>
       <c r="B20" s="7">
         <v>150</v>
@@ -942,24 +948,24 @@
         <v>31</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="17"/>
+      <c r="E20" s="16"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
-        <v>46194</v>
+        <v>46253</v>
       </c>
       <c r="B21" s="7">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="17"/>
+      <c r="E21" s="16"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
-        <v>46200</v>
+        <v>46256</v>
       </c>
       <c r="B22" s="7">
         <v>60</v>
@@ -968,20 +974,20 @@
         <v>29</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="17"/>
+      <c r="E22" s="16"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
-        <v>46201</v>
+        <v>46256</v>
       </c>
       <c r="B23" s="7">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>30</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="17"/>
+      <c r="E23" s="16"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" s="4">

--- a/planning tm.xlsx
+++ b/planning tm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bilal\jeu-unity\dossier-TM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76D569B-0851-415E-945F-F1E6FDFF1749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A8FFC2-D7D3-453A-BD31-65643B0F0159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="375" windowWidth="19185" windowHeight="10905" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
+    <workbookView xWindow="15" yWindow="1095" windowWidth="19185" windowHeight="10905" xr2:uid="{140D45C0-4E83-46EB-81B1-32109DB4487A}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>planning tm</t>
   </si>
@@ -128,9 +128,6 @@
     <t>animer saut et attaque de base</t>
   </si>
   <si>
-    <t>animer attaque spéciale au premier personnage</t>
-  </si>
-  <si>
     <t>implémenter animation de saut et attaques sur unity</t>
   </si>
   <si>
@@ -141,6 +138,18 @@
   </si>
   <si>
     <t>180 ou plus</t>
+  </si>
+  <si>
+    <t>au plus tard à la fin du mois d’août ; dans le cas de travaux pratiques ou créatifs, le travail est réalisé et une première version du commentaire écrit est produite.</t>
+  </si>
+  <si>
+    <t>Remettre jeu-vidéo et première version commentaire</t>
+  </si>
+  <si>
+    <t>mardi après les vacances d'automne, à 7h30 à l’aula</t>
+  </si>
+  <si>
+    <t>animer attaque spéciale au premier personnage et projectile</t>
   </si>
 </sst>
 </file>
@@ -150,7 +159,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,8 +189,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -226,19 +242,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -296,16 +306,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -350,10 +360,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}" name="Tableau1" displayName="Tableau1" ref="A2:E26" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
-  <autoFilter ref="A2:E26" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E25">
-    <sortCondition ref="A2:A25"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}" name="Tableau1" displayName="Tableau1" ref="A2:E27" totalsRowShown="0" headerRowDxfId="6" dataDxfId="5">
+  <autoFilter ref="A2:E27" xr:uid="{316CD99A-715F-4BE4-BD40-54C58784FC9B}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:E27">
+    <sortCondition ref="A2:A27"/>
   </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{71A8CFFA-D8D8-4528-9B87-104437A98853}" name="date" dataDxfId="4"/>
@@ -683,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A99B05EE-3531-444B-9158-CBFCD187C5CE}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.73046875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="30.265625" style="1" customWidth="1"/>
@@ -922,20 +932,20 @@
         <v>26</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="17"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="1">
         <v>46248</v>
       </c>
-      <c r="B19" s="15" t="s">
-        <v>33</v>
+      <c r="B19" s="14" t="s">
+        <v>32</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="14"/>
+      <c r="E19" s="17"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="1">
@@ -945,10 +955,10 @@
         <v>150</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="16"/>
+      <c r="E20" s="15"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="1">
@@ -961,7 +971,7 @@
         <v>28</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="16"/>
+      <c r="E21" s="15"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="1">
@@ -971,10 +981,10 @@
         <v>60</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="16"/>
+      <c r="E22" s="15"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="1">
@@ -984,41 +994,55 @@
         <v>30</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="16"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="E23" s="15"/>
+    </row>
+    <row r="24" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A24" s="4">
-        <v>46307</v>
+        <v>46264</v>
       </c>
       <c r="B24" s="7"/>
-      <c r="C24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="3"/>
+      <c r="C24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="4">
+        <v>46308</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A26" s="4">
         <v>46357</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B26" s="7">
         <v>30</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="B26" s="7">
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="7">
         <v>60</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
